--- a/implementation_evaluation_forms/033_hospital_ai_training_initiative_evaluation_form--implementation_evaluation_forms.xlsx
+++ b/implementation_evaluation_forms/033_hospital_ai_training_initiative_evaluation_form--implementation_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,35 +520,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Overall Experience</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>primary_goals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Primary Goals and Objectives</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>ai_model_performance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>AI Model Performance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>note1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>note2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Note2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>note3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Note3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>note4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Note4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page4</t>
+          <t>note5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Note5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page2</t>
+          <t>note6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Note6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,63 +722,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page2</t>
+          <t>ai_model_comparison</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>AI Model Comparison</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page2</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Selected Model</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page3</t>
+          <t>note7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Note7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,21 +791,159 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page3</t>
+          <t>ai_model_satisfactory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>AI Model Performance Satisfactory</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>documentation_clarity</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Documentation Clarity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>success_rating</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Overall Success</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>improvement_suggestions</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Suggestions</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>interaction_frequency</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Interaction Frequency</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>model_recommendation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Model Recommendation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,51 +988,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>ai_model_performance_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ai_model</t>
+          <t>ai_model_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI Model</t>
+          <t>AI Model 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>ai_model_performance_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_1</t>
+          <t>ai_model_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Model 1</t>
+          <t>AI Model 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>ai_model_comparison_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_2</t>
+          <t>ai_model_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Model 2</t>
+          <t>AI Model 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ai_model_comparison_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ai_model_2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AI Model 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>selected_model_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ai_model_1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AI Model 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>selected_model_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ai_model_2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AI Model 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ai_model_satisfactory_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>satisfactory</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ai_model_satisfactory_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>unsatisfactory</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unsatisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>success_rating_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>satisfactory</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>success_rating_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>unsatisfactory</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
